--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/UTAH_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/UTAH_2020.xlsx
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C72">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C152">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C194">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C218">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C226">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C232">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C311">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C344">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C348">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C444">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C605">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C618">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C627">
